--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6184-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6184-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{48D7424E-37BD-45BC-803F-B0C13BE171F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3D3A426-EE7F-4B65-85DE-90CAD5337830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{3F902A68-41D5-4AE0-ACCA-09953A8E7DF4}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{0D520405-937A-4354-A465-DB5734206B46}"/>
   </bookViews>
   <sheets>
     <sheet name="6184-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1559,30 +1559,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FAF6200-88EB-4240-B84B-1D24EAC5E1C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0263C43E-CEAD-4923-A894-AF0C937A4C52}">
   <dimension ref="A1:X45"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1616,7 +1616,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1652,7 +1652,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1772,7 +1772,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="39">
         <v>2024</v>
       </c>
@@ -1990,7 +1990,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2023</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>5.89</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2284,7 +2284,7 @@
         <v>5.89</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="39">
         <v>2022</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2504,7 +2504,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2021</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="39">
         <v>2020</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>29</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3166,7 +3166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2019</v>
       </c>
@@ -3238,7 +3238,7 @@
         <v>8.1199999999999992</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <v>2018</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>7.35</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2017</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>7.46</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="39">
         <v>2016</v>
       </c>
@@ -3454,7 +3454,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2015</v>
       </c>
@@ -3526,7 +3526,7 @@
         <v>5.73</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2014</v>
       </c>
@@ -3598,7 +3598,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2013</v>
       </c>
@@ -3670,7 +3670,7 @@
         <v>5.15</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="39">
         <v>2012</v>
       </c>
@@ -3742,7 +3742,7 @@
         <v>5.98</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>2011</v>
       </c>
@@ -3814,7 +3814,7 @@
         <v>7.54</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="41">
         <v>2010</v>
       </c>
@@ -3886,7 +3886,7 @@
         <v>7.66</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="43"/>
       <c r="B34" s="44"/>
       <c r="C34" s="20" t="s">
@@ -3914,7 +3914,7 @@
       <c r="W34" s="50"/>
       <c r="X34" s="46"/>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>2009</v>
       </c>
@@ -3986,7 +3986,7 @@
         <v>7.68</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="39">
         <v>2008</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>9.02</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>2007</v>
       </c>
@@ -4130,7 +4130,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="39">
         <v>2006</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>2005</v>
       </c>
@@ -4274,7 +4274,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="39">
         <v>2004</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>2003</v>
       </c>
@@ -4418,7 +4418,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="39">
         <v>2002</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>9.06</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37">
         <v>2001</v>
       </c>
@@ -4562,7 +4562,7 @@
         <v>7.81</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="39">
         <v>2000</v>
       </c>
@@ -4634,7 +4634,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="37" t="s">
         <v>62</v>
       </c>
